--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,90 +683,90 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=f158725620104e0c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d503c411915ae2d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,169 +1956,169 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Java Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a24b1c6ccb2c07f0</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,81 +2127,81 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Product Engineer TS Advanced Therapies</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,242 +2246,242 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Java Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a24b1c6ccb2c07f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Integration Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,242 +2666,242 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>El Paso Electric</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TapestryHealth</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>El Paso Electric</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,94 +3401,94 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,102 +3716,102 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Database Administrator - Philippines Only</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,54 +3891,54 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3947,11 +3947,11 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,75 +3961,705 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Senior Data Scientist/Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Java AI / ML Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Stockbridge, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FDE-Priniciple Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>CHS Corporate</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D121" t="n">
         <v>10.4</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Product Engineer TS Advanced Therapies</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Product Engineer TS Advanced Therapies</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,52 +2236,52 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Integration Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Integration Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>TapestryHealth</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TapestryHealth</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,69 +3006,69 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>El Paso Electric</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>El Paso Electric</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,69 +3426,69 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Administrator - Philippines Only</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Database Administrator - Philippines Only</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,77 +3986,77 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4520,146 +4520,6 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>FDE-Priniciple Software Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Enterprise Data Scientist – Human Capital</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CHS Corporate</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2533,12 +2533,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=819cd5adcc2e0b09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e84e96929c83510</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=d998781e3cf3685f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,54 +2666,54 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac64f3f2364b393c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=d57732575beb7281</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,116 +2722,116 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=71c3367f7265b4b1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8596280ccc1b4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=77bf277781b84f2f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=cecc27559ccd2adb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TapestryHealth</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec353d7c4d811e7c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b94def02b01e20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=a20a868ac55bf7b5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=92e0b50eaa73d1db</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d96dc2696b88bbb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3538c2508a18a51</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=17d3094fab7028db</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a4272756cee81a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=96f91ac51871dc56</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>El Paso Electric</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,54 +3296,54 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3352,46 +3352,46 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>TapestryHealth</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,137 +3751,137 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Administrator - Philippines Only</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>El Paso Electric</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,137 +3996,137 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,102 +4381,102 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Database Administrator - Philippines Only</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,40 +4486,635 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TomorrowNow</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist/Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Java AI / ML Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Stockbridge, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FDE-Priniciple Software Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>CHS Corporate</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D134" t="n">
         <v>10.4</v>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Product Engineer TS Advanced Therapies</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Product Engineer TS Advanced Therapies</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,52 +2236,52 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Integration Consultant</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Integration Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819cd5adcc2e0b09</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e84e96929c83510</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d998781e3cf3685f</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac64f3f2364b393c</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57732575beb7281</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c3367f7265b4b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,116 +2757,116 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8596280ccc1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bf277781b84f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecc27559ccd2adb</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec353d7c4d811e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TapestryHealth</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b94def02b01e20</t>
+          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20a868ac55bf7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e0b50eaa73d1db</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d96dc2696b88bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3538c2508a18a51</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d3094fab7028db</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a4272756cee81a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f91ac51871dc56</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,137 +3296,137 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>El Paso Electric</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TapestryHealth</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,172 +3751,172 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Database Administrator - Philippines Only</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>El Paso Electric</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,137 +3996,137 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,137 +4311,137 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Database Administrator - Philippines Only</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4485,636 +4485,6 @@
         </is>
       </c>
       <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TomorrowNow</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist/Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Java AI / ML Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer - Intern</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Stockbridge, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>(USA) Senior, Data Scientist</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Sam's Club</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Databases</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Security Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>FDE-Priniciple Software Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Enterprise Data Scientist – Human Capital</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>CHS Corporate</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Java Architect</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a24b1c6ccb2c07f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Integration Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92a4a8f000f1fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,54 +2526,54 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>TapestryHealth</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TapestryHealth</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>APPLICATION ARCHITECT- ASSOC -SR</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>El Paso Electric</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b19aee7bc7fb14a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Database Administrator - Philippines Only</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Administrator - Philippines Only</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9c277b4c81cb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4415,76 +4415,6 @@
         </is>
       </c>
       <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Enterprise Data Scientist – Human Capital</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CHS Corporate</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GenAI Architect</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d503c411915ae2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Product Engineer TS Advanced Therapies</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,52 +2271,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,52 +2481,52 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TapestryHealth</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, Splunk, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20395ed19d8168b</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI ML Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Administrator - Philippines Only</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, SQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c879d745e2848</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,112 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Enterprise Data Scientist – Human Capital</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>CHS Corporate</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,42 +3846,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,50 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27398865f051a625</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f88eed34169f4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,129 +531,129 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=27398865f051a625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ramsey, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f158725620104e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=f158725620104e0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
@@ -1961,29 +1961,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,77 +2306,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,42 +2596,42 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,29 +2691,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Dhara Consulting Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,77 +3356,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3881,42 +3881,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,137 +3926,137 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,262 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FDE-Priniciple Software Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,35 +923,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8078d1ebfe9d1942</t>
         </is>
       </c>
     </row>
@@ -2603,35 +2603,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Dhara Consulting Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dhara Consulting Group</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,49 +3156,49 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
@@ -4557,41 +4557,6 @@
       <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>FDE-Priniciple Software Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,12 +1273,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,69 +1291,69 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,52 +3566,52 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Business &amp; Quality Systems Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Intelitek Solutions</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=6e113dbede4e687a</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,15 +4546,50 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,47 +753,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f158725620104e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078d1ebfe9d1942</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,87 +1011,87 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
@@ -1103,47 +1103,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,94 +1256,94 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,94 +1826,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,104 +2341,104 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,104 +2516,104 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Dhara Consulting Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dhara Consulting Group</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
@@ -3093,87 +3093,87 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
@@ -3221,29 +3221,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,112 +3426,112 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3951,77 +3951,77 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Business &amp; Quality Systems Analyst</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Intelitek Solutions</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e113dbede4e687a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Business &amp; Quality Systems Analyst</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Intelitek Solutions</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, pytest</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e113dbede4e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4345,251 +4345,6 @@
         </is>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Databases</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Security Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>FDE-Priniciple Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,49 +1791,49 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,52 +2306,52 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,69 +3391,69 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,69 +3916,69 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business &amp; Quality Systems Analyst</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Intelitek Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e113dbede4e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,76 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,69 +521,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27398865f051a625</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>Associate Data Engineer - Databricks &amp; GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=bafb0baf34406e6c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,139 +591,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Ramsey, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
@@ -1068,47 +1068,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,29 +1221,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,122 +1256,122 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=e86a9395e17960c1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,49 +1791,49 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,104 +2236,104 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,104 +2446,104 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dhara Consulting Group</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,137 +2946,137 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,174 +3251,174 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=555204ef177ab237</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,172 +3716,172 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Industrial Applications Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>All American Poly</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a1080b879ebef05</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, GCP, Scala, ETL, MLOps, MLflow, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e37ba368e6b8a1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4205,76 +4205,6 @@
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,87 +538,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Databricks &amp; GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafb0baf34406e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>Associate Data Engineer - Databricks &amp; GCP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=bafb0baf34406e6c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,192 +626,192 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
@@ -823,55 +823,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Ramsey, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,77 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,164 +1196,164 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86a9395e17960c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,147 +1361,147 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,129 +1546,129 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,137 +1826,137 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,199 +1966,199 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,242 +2351,242 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,207 +2946,207 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,172 +3156,172 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555204ef177ab237</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,42 +3331,42 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
@@ -3378,257 +3378,257 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,49 +3751,49 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,120 +3803,120 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Logz.io</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Industrial Applications Developer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>All American Poly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,137 +3926,137 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1080b879ebef05</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, ETL, MLOps, MLflow, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e37ba368e6b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,112 +4101,602 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae5b1bbe9c75404</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>OCI Infrastructure Operations Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c83f36c42f90974a</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
         <v>10.4</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NELSON Worldwide</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SRE Engineer with Spanish/Portuguese</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Stockbridge, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,199 +881,199 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
@@ -1313,47 +1313,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,104 +1571,104 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,122 +2726,122 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,94 +3216,94 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,42 +3566,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,29 +3706,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f54039560a6f8280</t>
         </is>
       </c>
     </row>
@@ -4178,52 +4178,52 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OCI Infrastructure Operations Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83f36c42f90974a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,24 +4336,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,50 +4651,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,174 +906,174 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,104 +1571,104 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c56a9ffac444186</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Architect - Minneapolis, MN</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Data Architect - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,129 +3401,129 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,42 +3566,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,172 +3646,172 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,49 +3821,49 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54039560a6f8280</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=71d009d7cafef710</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb7d6f981c89a53</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Activate Care</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,102 +4171,102 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae5b1bbe9c75404</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logz.io</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,234 +4276,234 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,15 +4651,365 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,104 +731,104 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,29 +1606,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,38 +1637,38 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=7c56a9ffac444186</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c56a9ffac444186</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect - Minneapolis, MN</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,29 +3321,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,94 +3436,94 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,59 +3821,59 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=71d009d7cafef710</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb7d6f981c89a53</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Activate Care</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Logz.io</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d009d7cafef710</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb7d6f981c89a53</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Activate Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,24 +4231,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,24 +4336,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,19 +4486,19 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,24 +4616,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,147 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Databases</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Security Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TowneBank</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Diverse Lynx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c56a9ffac444186</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,129 +2001,129 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8687d4f949f812</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,112 +2481,112 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
         </is>
       </c>
     </row>
@@ -2713,20 +2713,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8987d00ce94ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf2c43159b0243f</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Architect - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Architect - Minneapolis, MN</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,129 +3321,129 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,52 +3706,52 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Activate Care</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Logz.io</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d009d7cafef710</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb7d6f981c89a53</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Activate Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
@@ -4528,17 +4528,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,24 +4546,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,15 +4861,190 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Security Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=51b0c228ba35d8c5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,129 +1266,129 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, Vertex AI, Scala, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b84fd7269e4e8d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=68da0b82e0c0971f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,29 +1781,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Diverse Lynx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,104 +1921,104 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,77 +2411,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8f95c86a9a4e627</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Data Architect - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect - Minneapolis, MN</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,42 +3286,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Vimly Benefit Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ca24307b6c2a4b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Senior Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,42 +3706,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,59 +3751,59 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=555204ef177ab237</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Activate Care</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Activate Care</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Logz.io</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae5b1bbe9c75404</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>OCI Infrastructure Operations Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=c83f36c42f90974a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior Consultant - Data Engineering &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Black &amp; Veatch</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c1aa86a59e2c6c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer II, Databases</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Security Software Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,17 +5036,332 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5fe6313bc377228</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Business Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Texas Capital Bank</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9813268f71a7390</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Databases</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-11.xlsx
+++ b/results/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8f5d1958986efa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0eb1930f6c3830</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6b4c094d34de4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae79c8e8bf869344</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,137 +916,137 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (HYBRID-CHARLOTTE, NC)</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, IAM, Azure, Spark</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe6c8c4b0190d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b0c228ba35d8c5</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,52 +1361,52 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
@@ -1418,82 +1418,82 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, Vertex AI, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b84fd7269e4e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68da0b82e0c0971f</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diverse Lynx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,77 +2411,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Celero Commerce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8f95c86a9a4e627</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect - Minneapolis, MN</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feba864f904f24</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Officer, Data Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988b83e5611aee95</t>
+          <t>https://www.indeed.com/viewjob?jk=91029e440b1faee3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vimly Benefit Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ca24307b6c2a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,59 +3751,59 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555204ef177ab237</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802074095bbf141a</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Developer II - Data Science &amp; Enterprise Data Platform Development</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Activate Care</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Snowflake, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd0f856172e7cf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, YARN, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
@@ -4423,25 +4423,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,59 +4486,59 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae5b1bbe9c75404</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OCI Infrastructure Operations Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stockbridge, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83f36c42f90974a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Stockbridge, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdee89b0e47d15e1</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Engineering &amp; Business Intelligence</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Black &amp; Veatch</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c1aa86a59e2c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer II, Databases</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
+          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fe6313bc377228</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,227 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>LG Ad Solutions</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9813268f71a7390</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Kingston, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Databases</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
